--- a/字辈排行.xlsx
+++ b/字辈排行.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\P1368\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\宁海下枫槎村网站\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457DCF2B-4719-474B-981B-EFCEAE0B6545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{825D9186-F60D-49E6-83BA-B1BA57EBEB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,30 +33,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="89">
   <si>
     <t>石马枫槎世系行第对照表</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -443,12 +421,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -478,15 +474,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -769,511 +780,548 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr defaultRowHeight="33" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="33.88671875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.21875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="24.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="33.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" style="1" customWidth="1"/>
+    <col min="5" max="7" width="8.88671875" style="1"/>
+    <col min="8" max="10" width="11.5546875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="2.6640625" style="3" customWidth="1"/>
+    <col min="12" max="13" width="11.5546875" style="3" customWidth="1"/>
+    <col min="14" max="14" width="18.21875" style="3" customWidth="1"/>
+    <col min="15" max="15" width="5.88671875" style="3" customWidth="1"/>
+    <col min="16" max="16" width="18.21875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="18.6640625" style="3" customWidth="1"/>
+    <col min="18" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
     </row>
     <row r="2" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="2">
         <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="2">
         <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="2">
         <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="2">
         <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="2">
         <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="2">
         <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3" t="s">
+      <c r="A24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3" t="s">
+      <c r="A25" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="2">
         <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3" t="s">
+      <c r="A26" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="2">
         <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3" t="s">
+      <c r="A27" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3" t="s">
+      <c r="A28" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="2">
         <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3" t="s">
+      <c r="A29" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="2">
         <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3" t="s">
+      <c r="A30" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="2">
         <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3" t="s">
+      <c r="A31" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="2">
         <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3" t="s">
+      <c r="A32" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="2">
         <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3" t="s">
+      <c r="A33" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="2">
         <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3" t="s">
+      <c r="A34" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="2">
         <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3" t="s">
+      <c r="A35" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="2">
         <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3" t="s">
+      <c r="A36" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="2">
         <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3" t="s">
+      <c r="A37" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="2">
         <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3" t="s">
+      <c r="A38" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D38" s="3" cm="1">
-        <f t="array" aca="1" ref="D38" ca="1">A1:D3851</f>
-        <v>0</v>
+      <c r="D38" s="2">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
